--- a/data/nzd0034/nzd0034.xlsx
+++ b/data/nzd0034/nzd0034.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I510"/>
+  <dimension ref="A1:I514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17266,6 +17266,138 @@
         <v>384.68</v>
       </c>
       <c r="I510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="C511" t="n">
+        <v>382.57</v>
+      </c>
+      <c r="D511" t="n">
+        <v>379.06</v>
+      </c>
+      <c r="E511" t="n">
+        <v>381.68</v>
+      </c>
+      <c r="F511" t="n">
+        <v>385.55</v>
+      </c>
+      <c r="G511" t="n">
+        <v>390.76</v>
+      </c>
+      <c r="H511" t="n">
+        <v>384.49</v>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>384.19</v>
+      </c>
+      <c r="C512" t="n">
+        <v>382.54</v>
+      </c>
+      <c r="D512" t="n">
+        <v>379.48</v>
+      </c>
+      <c r="E512" t="n">
+        <v>381.74</v>
+      </c>
+      <c r="F512" t="n">
+        <v>385.5</v>
+      </c>
+      <c r="G512" t="n">
+        <v>390.35</v>
+      </c>
+      <c r="H512" t="n">
+        <v>383.98</v>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="C513" t="n">
+        <v>382.54</v>
+      </c>
+      <c r="D513" t="n">
+        <v>379.57</v>
+      </c>
+      <c r="E513" t="n">
+        <v>382.04</v>
+      </c>
+      <c r="F513" t="n">
+        <v>386.16</v>
+      </c>
+      <c r="G513" t="n">
+        <v>390.62</v>
+      </c>
+      <c r="H513" t="n">
+        <v>384.29</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>391.45</v>
+      </c>
+      <c r="C514" t="n">
+        <v>381.8</v>
+      </c>
+      <c r="D514" t="n">
+        <v>378.94</v>
+      </c>
+      <c r="E514" t="n">
+        <v>381.97</v>
+      </c>
+      <c r="F514" t="n">
+        <v>385.46</v>
+      </c>
+      <c r="G514" t="n">
+        <v>390.14</v>
+      </c>
+      <c r="H514" t="n">
+        <v>383.82</v>
+      </c>
+      <c r="I514" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17282,7 +17414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B574"/>
+  <dimension ref="A1:B578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23025,6 +23157,46 @@
       </c>
       <c r="B574" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23193,28 +23365,28 @@
         <v>0.1907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1921482480149379</v>
+        <v>0.172588927439221</v>
       </c>
       <c r="J2" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="K2" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01137457131930486</v>
+        <v>0.009264460553119025</v>
       </c>
       <c r="M2" t="n">
-        <v>11.0252004988353</v>
+        <v>11.0489671734998</v>
       </c>
       <c r="N2" t="n">
-        <v>195.6973708591891</v>
+        <v>195.7900759818184</v>
       </c>
       <c r="O2" t="n">
-        <v>13.9891876411459</v>
+        <v>13.99250070508551</v>
       </c>
       <c r="P2" t="n">
-        <v>394.9874121322387</v>
+        <v>395.190306236723</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23271,28 +23443,28 @@
         <v>0.118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02058542097362856</v>
+        <v>0.009247622922040708</v>
       </c>
       <c r="J3" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="K3" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004853609106804102</v>
+        <v>9.860469669309424e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>5.795425621615403</v>
+        <v>5.797538969393395</v>
       </c>
       <c r="N3" t="n">
-        <v>53.21808739615205</v>
+        <v>53.30242994508189</v>
       </c>
       <c r="O3" t="n">
-        <v>7.29507281637079</v>
+        <v>7.300851316461793</v>
       </c>
       <c r="P3" t="n">
-        <v>389.8979535596885</v>
+        <v>390.01559554877</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23349,28 +23521,28 @@
         <v>0.1162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09392024127201945</v>
+        <v>0.08209830645339709</v>
       </c>
       <c r="J4" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="K4" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01214230977101294</v>
+        <v>0.009334073802559129</v>
       </c>
       <c r="M4" t="n">
-        <v>5.408814522145562</v>
+        <v>5.424178873409445</v>
       </c>
       <c r="N4" t="n">
-        <v>44.03310150412152</v>
+        <v>44.2378555093461</v>
       </c>
       <c r="O4" t="n">
-        <v>6.635744231367083</v>
+        <v>6.651154449367877</v>
       </c>
       <c r="P4" t="n">
-        <v>385.2054275209953</v>
+        <v>385.3275071023785</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23427,28 +23599,28 @@
         <v>0.0878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09347127851198973</v>
+        <v>0.0832716486518239</v>
       </c>
       <c r="J5" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="K5" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009871104405382858</v>
+        <v>0.007913275701240563</v>
       </c>
       <c r="M5" t="n">
-        <v>6.164971435078875</v>
+        <v>6.17447881351861</v>
       </c>
       <c r="N5" t="n">
-        <v>53.77125293523674</v>
+        <v>53.7597624381382</v>
       </c>
       <c r="O5" t="n">
-        <v>7.332888444210558</v>
+        <v>7.332104911833859</v>
       </c>
       <c r="P5" t="n">
-        <v>386.6495095308521</v>
+        <v>386.7548338005984</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23505,28 +23677,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06811323052309259</v>
+        <v>0.05647248081011877</v>
       </c>
       <c r="J6" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="K6" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005161248691364917</v>
+        <v>0.003574698789398423</v>
       </c>
       <c r="M6" t="n">
-        <v>6.009408967349581</v>
+        <v>6.037691500980211</v>
       </c>
       <c r="N6" t="n">
-        <v>54.86920478031136</v>
+        <v>54.97290656994468</v>
       </c>
       <c r="O6" t="n">
-        <v>7.407375026303945</v>
+        <v>7.41437162340442</v>
       </c>
       <c r="P6" t="n">
-        <v>392.1789838484265</v>
+        <v>392.2991909914854</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23583,28 +23755,28 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08603182523902264</v>
+        <v>0.07397551362492681</v>
       </c>
       <c r="J7" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="K7" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009881345995545132</v>
+        <v>0.007347469384947791</v>
       </c>
       <c r="M7" t="n">
-        <v>5.246629497369252</v>
+        <v>5.278487535241823</v>
       </c>
       <c r="N7" t="n">
-        <v>45.5048000807549</v>
+        <v>45.71988411458182</v>
       </c>
       <c r="O7" t="n">
-        <v>6.745724577890421</v>
+        <v>6.761648032438676</v>
       </c>
       <c r="P7" t="n">
-        <v>396.7927966119701</v>
+        <v>396.9172972912086</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23661,28 +23833,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01436272253326647</v>
+        <v>0.004831938124382502</v>
       </c>
       <c r="J8" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="K8" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003307617865988544</v>
+        <v>3.768378581270326e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.819568889815709</v>
+        <v>4.833962066613346</v>
       </c>
       <c r="N8" t="n">
-        <v>38.25448334140854</v>
+        <v>38.31258974978904</v>
       </c>
       <c r="O8" t="n">
-        <v>6.185020884476344</v>
+        <v>6.189716451485403</v>
       </c>
       <c r="P8" t="n">
-        <v>390.5958845527433</v>
+        <v>390.6943055446023</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23720,7 +23892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I510"/>
+  <dimension ref="A1:I514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47685,6 +47857,194 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-34.94349227473797,173.5732854813782</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-34.94401184531314,173.5738020088551</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-34.944388753263134,173.57451880473735</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-34.94466625914225,173.57532792221693</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-34.94484956294092,173.5761682143003</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-34.944930707779996,173.57700528889708</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-34.944924209174545,173.57784917982144</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-34.943472328003025,173.57331644496003</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-34.94401204998151,173.5738017940326</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-34.94438538825615,173.57452091516876</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-34.94466575396125,173.5753281574222</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-34.944850000596254,173.57616808275046</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-34.94493440114923,173.577005088374</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-34.944928788347646,173.57784969499036</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-34.943447825178666,173.57335448098286</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-34.94401204998151,173.5738017940326</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-34.94438466718322,173.57452136740403</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-34.94466322805629,173.57532933344862</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-34.94484422354579,173.57616981920825</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-34.94493196893046,173.5770052204258</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-34.94492600492872,173.57784938184844</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-34.94343199001379,173.573379062074</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-34.944017098467626,173.57379649507698</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-34.944389714693706,173.57451820175692</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-34.94466381743412,173.57532905904245</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-34.94485035072052,173.57616797751058</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-34.94493629287494,173.57700498566703</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-34.944930224950966,173.57784985661198</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0034/nzd0034.xlsx
+++ b/data/nzd0034/nzd0034.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I514"/>
+  <dimension ref="A1:I519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17398,6 +17398,171 @@
         <v>383.82</v>
       </c>
       <c r="I514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>394.5</v>
+      </c>
+      <c r="C515" t="n">
+        <v>381.73</v>
+      </c>
+      <c r="D515" t="n">
+        <v>379.36</v>
+      </c>
+      <c r="E515" t="n">
+        <v>382.42</v>
+      </c>
+      <c r="F515" t="n">
+        <v>385.46</v>
+      </c>
+      <c r="G515" t="n">
+        <v>390.11</v>
+      </c>
+      <c r="H515" t="n">
+        <v>383.86</v>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>397.81</v>
+      </c>
+      <c r="C516" t="n">
+        <v>381.81</v>
+      </c>
+      <c r="D516" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="E516" t="n">
+        <v>382.58</v>
+      </c>
+      <c r="F516" t="n">
+        <v>386.21</v>
+      </c>
+      <c r="G516" t="n">
+        <v>390.31</v>
+      </c>
+      <c r="H516" t="n">
+        <v>384.09</v>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>401.93</v>
+      </c>
+      <c r="C517" t="n">
+        <v>382.57</v>
+      </c>
+      <c r="D517" t="n">
+        <v>380.31</v>
+      </c>
+      <c r="E517" t="n">
+        <v>383.38</v>
+      </c>
+      <c r="F517" t="n">
+        <v>386.96</v>
+      </c>
+      <c r="G517" t="n">
+        <v>390.92</v>
+      </c>
+      <c r="H517" t="n">
+        <v>384.65</v>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>404.14</v>
+      </c>
+      <c r="C518" t="n">
+        <v>382.69</v>
+      </c>
+      <c r="D518" t="n">
+        <v>380.13</v>
+      </c>
+      <c r="E518" t="n">
+        <v>383.24</v>
+      </c>
+      <c r="F518" t="n">
+        <v>387.1</v>
+      </c>
+      <c r="G518" t="n">
+        <v>390.74</v>
+      </c>
+      <c r="H518" t="n">
+        <v>384.37</v>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>406.03</v>
+      </c>
+      <c r="C519" t="n">
+        <v>382.95</v>
+      </c>
+      <c r="D519" t="n">
+        <v>380.39</v>
+      </c>
+      <c r="E519" t="n">
+        <v>383.54</v>
+      </c>
+      <c r="F519" t="n">
+        <v>387.18</v>
+      </c>
+      <c r="G519" t="n">
+        <v>390.81</v>
+      </c>
+      <c r="H519" t="n">
+        <v>384.33</v>
+      </c>
+      <c r="I519" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17414,7 +17579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B578"/>
+  <dimension ref="A1:B583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23197,6 +23362,56 @@
       </c>
       <c r="B578" t="n">
         <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -23365,28 +23580,28 @@
         <v>0.1907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.172588927439221</v>
+        <v>0.1743608078289295</v>
       </c>
       <c r="J2" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K2" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009264460553119025</v>
+        <v>0.009626171845924958</v>
       </c>
       <c r="M2" t="n">
-        <v>11.0489671734998</v>
+        <v>10.98040403357129</v>
       </c>
       <c r="N2" t="n">
-        <v>195.7900759818184</v>
+        <v>194.0770888145358</v>
       </c>
       <c r="O2" t="n">
-        <v>13.99250070508551</v>
+        <v>13.93115532949568</v>
       </c>
       <c r="P2" t="n">
-        <v>395.190306236723</v>
+        <v>395.1717758718155</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23443,28 +23658,28 @@
         <v>0.118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009247622922040708</v>
+        <v>-0.004301145278511439</v>
       </c>
       <c r="J3" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K3" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="L3" t="n">
-        <v>9.860469669309424e-05</v>
+        <v>2.150441838288941e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>5.797538969393395</v>
+        <v>5.798209286127288</v>
       </c>
       <c r="N3" t="n">
-        <v>53.30242994508189</v>
+        <v>53.37798347164786</v>
       </c>
       <c r="O3" t="n">
-        <v>7.300851316461793</v>
+        <v>7.306023779844127</v>
       </c>
       <c r="P3" t="n">
-        <v>390.01559554877</v>
+        <v>390.1565963043276</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23521,28 +23736,28 @@
         <v>0.1162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08209830645339709</v>
+        <v>0.06917952438761994</v>
       </c>
       <c r="J4" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K4" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009334073802559129</v>
+        <v>0.006690929223868047</v>
       </c>
       <c r="M4" t="n">
-        <v>5.424178873409445</v>
+        <v>5.4343984928994</v>
       </c>
       <c r="N4" t="n">
-        <v>44.2378555093461</v>
+        <v>44.35216550872449</v>
       </c>
       <c r="O4" t="n">
-        <v>6.651154449367877</v>
+        <v>6.659742150318171</v>
       </c>
       <c r="P4" t="n">
-        <v>385.3275071023785</v>
+        <v>385.461316804503</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23599,28 +23814,28 @@
         <v>0.0878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0832716486518239</v>
+        <v>0.07309668761309535</v>
       </c>
       <c r="J5" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K5" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007913275701240563</v>
+        <v>0.006186975921543714</v>
       </c>
       <c r="M5" t="n">
-        <v>6.17447881351861</v>
+        <v>6.171786300247463</v>
       </c>
       <c r="N5" t="n">
-        <v>53.7597624381382</v>
+        <v>53.5776144520588</v>
       </c>
       <c r="O5" t="n">
-        <v>7.332104911833859</v>
+        <v>7.319673111011093</v>
       </c>
       <c r="P5" t="n">
-        <v>386.7548338005984</v>
+        <v>386.8602212276425</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23677,28 +23892,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05647248081011877</v>
+        <v>0.04413778913052334</v>
       </c>
       <c r="J6" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K6" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003574698789398423</v>
+        <v>0.002208743402364655</v>
       </c>
       <c r="M6" t="n">
-        <v>6.037691500980211</v>
+        <v>6.059237078987401</v>
       </c>
       <c r="N6" t="n">
-        <v>54.97290656994468</v>
+        <v>54.93856352172933</v>
       </c>
       <c r="O6" t="n">
-        <v>7.41437162340442</v>
+        <v>7.412055283234828</v>
       </c>
       <c r="P6" t="n">
-        <v>392.2991909914854</v>
+        <v>392.4269447267519</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23755,28 +23970,28 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07397551362492681</v>
+        <v>0.05977557017872234</v>
       </c>
       <c r="J7" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K7" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007347469384947791</v>
+        <v>0.004832743302915055</v>
       </c>
       <c r="M7" t="n">
-        <v>5.278487535241823</v>
+        <v>5.312900347080967</v>
       </c>
       <c r="N7" t="n">
-        <v>45.71988411458182</v>
+        <v>45.93159485571739</v>
       </c>
       <c r="O7" t="n">
-        <v>6.761648032438676</v>
+        <v>6.777285212805891</v>
       </c>
       <c r="P7" t="n">
-        <v>396.9172972912086</v>
+        <v>397.0643797612316</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23833,28 +24048,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004831938124382502</v>
+        <v>-0.00634431999719168</v>
       </c>
       <c r="J8" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K8" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="L8" t="n">
-        <v>3.768378581270326e-05</v>
+        <v>6.551903207185905e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>4.833962066613346</v>
+        <v>4.848505199946945</v>
       </c>
       <c r="N8" t="n">
-        <v>38.31258974978904</v>
+        <v>38.34740247388859</v>
       </c>
       <c r="O8" t="n">
-        <v>6.189716451485403</v>
+        <v>6.19252795503489</v>
       </c>
       <c r="P8" t="n">
-        <v>390.6943055446023</v>
+        <v>390.81006962264</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23892,7 +24107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I514"/>
+  <dimension ref="A1:I519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48045,6 +48260,241 @@
         </is>
       </c>
     </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-34.943415043603835,173.57340536814345</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-34.944017576027115,173.5737959938244</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-34.94438634968673,173.57452031218838</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-34.944660028576635,173.57533082308194</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-34.94485035072052,173.57616797751058</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-34.94493656312147,173.5770049709946</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-34.944929865800134,173.57784981620657</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-34.943396652575494,173.57343391668525</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-34.944017030244844,173.5737965666845</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-34.94438426658716,173.57452161864586</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-34.94465868142733,173.57533145029592</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-34.94484378589045,173.57616995075807</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-34.94493476147793,173.57700506881073</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-34.944927800682855,173.57784958387546</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-34.94337376101433,173.57346945140824</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-34.94401184531314,173.5738020088551</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-34.94437873836128,173.5745250857827</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-34.94465194568063,173.57533458636559</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-34.94483722106033,173.57617192400525</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-34.94492926646515,173.57700536715</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-34.944922772571225,173.57784901819983</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-34.94336148179887,173.57348851250148</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-34.944011026639686,173.57380286814512</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-34.944380180507174,173.57452418131226</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-34.94465312443631,173.57533403755343</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-34.944835995625375,173.5761722923447</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-34.94493088794434,173.5770052791155</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-34.94492528662705,173.57784930103765</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-34.943350980567025,173.57350481361289</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-34.94400925284719,173.57380472994012</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-34.944378097407565,173.57452548776956</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-34.94465059853129,173.57533521357945</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-34.94483529537682,173.57617250282436</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-34.9449302573691,173.57700531335112</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-34.94492564577788,173.57784934144306</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0034/nzd0034.xlsx
+++ b/data/nzd0034/nzd0034.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I519"/>
+  <dimension ref="A1:I522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17563,6 +17563,105 @@
         <v>384.33</v>
       </c>
       <c r="I519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>406.03</v>
+      </c>
+      <c r="C520" t="n">
+        <v>382.35</v>
+      </c>
+      <c r="D520" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="E520" t="n">
+        <v>382.97</v>
+      </c>
+      <c r="F520" t="n">
+        <v>386.72</v>
+      </c>
+      <c r="G520" t="n">
+        <v>390.66</v>
+      </c>
+      <c r="H520" t="n">
+        <v>384.16</v>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>407.01</v>
+      </c>
+      <c r="C521" t="n">
+        <v>382.58</v>
+      </c>
+      <c r="D521" t="n">
+        <v>380.04</v>
+      </c>
+      <c r="E521" t="n">
+        <v>383.15</v>
+      </c>
+      <c r="F521" t="n">
+        <v>386.68</v>
+      </c>
+      <c r="G521" t="n">
+        <v>390.54</v>
+      </c>
+      <c r="H521" t="n">
+        <v>384.22</v>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>410.13</v>
+      </c>
+      <c r="C522" t="n">
+        <v>382.91</v>
+      </c>
+      <c r="D522" t="n">
+        <v>380.15</v>
+      </c>
+      <c r="E522" t="n">
+        <v>383.65</v>
+      </c>
+      <c r="F522" t="n">
+        <v>386.94</v>
+      </c>
+      <c r="G522" t="n">
+        <v>390.94</v>
+      </c>
+      <c r="H522" t="n">
+        <v>384.48</v>
+      </c>
+      <c r="I522" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17579,7 +17678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B583"/>
+  <dimension ref="A1:B586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23412,6 +23511,36 @@
       </c>
       <c r="B583" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -23580,28 +23709,28 @@
         <v>0.1907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1743608078289295</v>
+        <v>0.1823304770976196</v>
       </c>
       <c r="J2" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K2" t="n">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009626171845924958</v>
+        <v>0.01061571001975992</v>
       </c>
       <c r="M2" t="n">
-        <v>10.98040403357129</v>
+        <v>10.9605059460779</v>
       </c>
       <c r="N2" t="n">
-        <v>194.0770888145358</v>
+        <v>193.3217717007499</v>
       </c>
       <c r="O2" t="n">
-        <v>13.93115532949568</v>
+        <v>13.90401998347061</v>
       </c>
       <c r="P2" t="n">
-        <v>395.1717758718155</v>
+        <v>395.088414658891</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23658,28 +23787,28 @@
         <v>0.118</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.004301145278511439</v>
+        <v>-0.01186286110559139</v>
       </c>
       <c r="J3" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K3" t="n">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="L3" t="n">
-        <v>2.150441838288941e-05</v>
+        <v>0.0001644563539261457</v>
       </c>
       <c r="M3" t="n">
-        <v>5.798209286127288</v>
+        <v>5.796450910044213</v>
       </c>
       <c r="N3" t="n">
-        <v>53.37798347164786</v>
+        <v>53.38301171110365</v>
       </c>
       <c r="O3" t="n">
-        <v>7.306023779844127</v>
+        <v>7.306367887747212</v>
       </c>
       <c r="P3" t="n">
-        <v>390.1565963043276</v>
+        <v>390.235661274766</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23736,28 +23865,28 @@
         <v>0.1162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06917952438761994</v>
+        <v>0.06175092104145619</v>
       </c>
       <c r="J4" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K4" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006690929223868047</v>
+        <v>0.005362008743290181</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4343984928994</v>
+        <v>5.439006313327334</v>
       </c>
       <c r="N4" t="n">
-        <v>44.35216550872449</v>
+        <v>44.4011837645213</v>
       </c>
       <c r="O4" t="n">
-        <v>6.659742150318171</v>
+        <v>6.663421325754608</v>
       </c>
       <c r="P4" t="n">
-        <v>385.461316804503</v>
+        <v>385.5386253224218</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23814,28 +23943,28 @@
         <v>0.0878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07309668761309535</v>
+        <v>0.06743807827251763</v>
       </c>
       <c r="J5" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K5" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006186975921543714</v>
+        <v>0.00531312830750863</v>
       </c>
       <c r="M5" t="n">
-        <v>6.171786300247463</v>
+        <v>6.167533433435789</v>
       </c>
       <c r="N5" t="n">
-        <v>53.5776144520588</v>
+        <v>53.44617113786241</v>
       </c>
       <c r="O5" t="n">
-        <v>7.319673111011093</v>
+        <v>7.310688827864473</v>
       </c>
       <c r="P5" t="n">
-        <v>386.8602212276425</v>
+        <v>386.9191065222974</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23892,28 +24021,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04413778913052334</v>
+        <v>0.03719917631966303</v>
       </c>
       <c r="J6" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K6" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002208743402364655</v>
+        <v>0.001580063034183343</v>
       </c>
       <c r="M6" t="n">
-        <v>6.059237078987401</v>
+        <v>6.069097213060922</v>
       </c>
       <c r="N6" t="n">
-        <v>54.93856352172933</v>
+        <v>54.88777460378606</v>
       </c>
       <c r="O6" t="n">
-        <v>7.412055283234828</v>
+        <v>7.408628388830557</v>
       </c>
       <c r="P6" t="n">
-        <v>392.4269447267519</v>
+        <v>392.4991537594082</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23970,28 +24099,28 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05977557017872234</v>
+        <v>0.05169702320394266</v>
       </c>
       <c r="J7" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K7" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004832743302915055</v>
+        <v>0.003631675350477037</v>
       </c>
       <c r="M7" t="n">
-        <v>5.312900347080967</v>
+        <v>5.331125290022357</v>
       </c>
       <c r="N7" t="n">
-        <v>45.93159485571739</v>
+        <v>46.0271528232776</v>
       </c>
       <c r="O7" t="n">
-        <v>6.777285212805891</v>
+        <v>6.784331420506931</v>
       </c>
       <c r="P7" t="n">
-        <v>397.0643797612316</v>
+        <v>397.148451518429</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24048,28 +24177,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.00634431999719168</v>
+        <v>-0.01278057570823043</v>
       </c>
       <c r="J8" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K8" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L8" t="n">
-        <v>6.551903207185905e-05</v>
+        <v>0.0002672583924053784</v>
       </c>
       <c r="M8" t="n">
-        <v>4.848505199946945</v>
+        <v>4.855673397433317</v>
       </c>
       <c r="N8" t="n">
-        <v>38.34740247388859</v>
+        <v>38.35513734746527</v>
       </c>
       <c r="O8" t="n">
-        <v>6.19252795503489</v>
+        <v>6.193152456339604</v>
       </c>
       <c r="P8" t="n">
-        <v>390.81006962264</v>
+        <v>390.8770501999051</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24107,7 +24236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I519"/>
+  <dimension ref="A1:I522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48495,6 +48624,147 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-34.943350980567025,173.57350481361289</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-34.94401334621444,173.57380043349</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-34.94438266420285,173.57452262361312</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-34.944655397750815,173.57533297912994</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-34.94483932180597,173.5761712925662</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-34.94493160860175,173.577005239989</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-34.9449271721689,173.57784951316603</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-34.94334553548298,173.57351326603938</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-34.944011777090346,173.5738020804626</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-34.94438090158012,173.57452372907704</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-34.94465388220782,173.5753336847456</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-34.94483967193024,173.57617118732634</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-34.94493268958787,173.57700518129934</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-34.944926633442655,173.57784945255793</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-34.94332820010954,173.57354017579792</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-34.94400952573835,173.57380444351014</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-34.94438002026875,173.574524281809</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-34.9446496723661,173.575335644789</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-34.94483739612246,173.57617187138533</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-34.94492908630081,173.57700537693162</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>-34.94492429896226,173.5778491899228</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
